--- a/Result/profitability/4420.xlsx
+++ b/Result/profitability/4420.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.53</v>
       </c>
       <c r="M2" t="n">
-        <v>1.61625</v>
+        <v>0.97875</v>
       </c>
       <c r="N2" t="n">
-        <v>4.2675</v>
+        <v>5.225</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.38</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9299999999999999</v>
+        <v>0.92125</v>
       </c>
       <c r="N3" t="n">
-        <v>5.38875</v>
+        <v>6.20875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.3</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8625</v>
+        <v>0.34875</v>
       </c>
       <c r="N4" t="n">
-        <v>6.1825</v>
+        <v>6.8075</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.03</v>
       </c>
       <c r="M5" t="n">
-        <v>0.25625</v>
+        <v>0.3225</v>
       </c>
       <c r="N5" t="n">
-        <v>6.145</v>
+        <v>6.83</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.08</v>
       </c>
       <c r="M6" t="n">
-        <v>0.21625</v>
+        <v>0.3</v>
       </c>
       <c r="N6" t="n">
-        <v>5.787500000000001</v>
+        <v>6.4825</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.36</v>
       </c>
       <c r="M7" t="n">
-        <v>0.24875</v>
+        <v>0.3075</v>
       </c>
       <c r="N7" t="n">
-        <v>7.05375</v>
+        <v>7.50125</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.4</v>
       </c>
       <c r="M8" t="n">
-        <v>0.26125</v>
+        <v>0.33625</v>
       </c>
       <c r="N8" t="n">
-        <v>8.141249999999999</v>
+        <v>8.414999999999999</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1521,7 +1521,7 @@
         <v>0.2825</v>
       </c>
       <c r="N9" t="n">
-        <v>9.1675</v>
+        <v>9.167499999999999</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>4420</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>249</v>
+      </c>
+      <c r="D75" t="n">
+        <v>228</v>
+      </c>
+      <c r="E75" t="n">
+        <v>21</v>
+      </c>
+      <c r="F75" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="G75" t="n">
+        <v>9</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>3.52%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>29</v>
+      </c>
+      <c r="J75" t="n">
+        <v>37</v>
+      </c>
+      <c r="K75" t="n">
+        <v>31</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.64625</v>
+      </c>
+      <c r="N75" t="n">
+        <v>3.74625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="X75" t="n">
+        <v>3.529411764705882</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.3613861386138615</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>2.208333333333333</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>1.978339350180506</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
